--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty FMCG ETF.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty FMCG ETF.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="74">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Nifty FMCG ETF</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -85,6 +85,21 @@
     <t>Food Products</t>
   </si>
   <si>
+    <t>Tata Consumer Products Ltd.</t>
+  </si>
+  <si>
+    <t>INE192A01025</t>
+  </si>
+  <si>
+    <t>Agricultural Food &amp; Other Products</t>
+  </si>
+  <si>
+    <t>Britannia Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE216A01030</t>
+  </si>
+  <si>
     <t>Varun Beverages Ltd.</t>
   </si>
   <si>
@@ -94,21 +109,6 @@
     <t>Beverages</t>
   </si>
   <si>
-    <t>Tata Consumer Products Ltd.</t>
-  </si>
-  <si>
-    <t>INE192A01025</t>
-  </si>
-  <si>
-    <t>Agricultural Food &amp; Other Products</t>
-  </si>
-  <si>
-    <t>Britannia Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE216A01030</t>
-  </si>
-  <si>
     <t>Godrej Consumer Products Ltd.</t>
   </si>
   <si>
@@ -124,18 +124,18 @@
     <t>INE854D01024</t>
   </si>
   <si>
+    <t>Marico Ltd.</t>
+  </si>
+  <si>
+    <t>INE196A01026</t>
+  </si>
+  <si>
     <t>Colgate - Palmolive (India) Ltd.</t>
   </si>
   <si>
     <t>INE259A01022</t>
   </si>
   <si>
-    <t>Marico Ltd.</t>
-  </si>
-  <si>
-    <t>INE196A01026</t>
-  </si>
-  <si>
     <t>Dabur India Ltd.</t>
   </si>
   <si>
@@ -148,31 +148,22 @@
     <t>INE944F01028</t>
   </si>
   <si>
+    <t>Patanjali Foods Ltd.</t>
+  </si>
+  <si>
+    <t>INE619A01035</t>
+  </si>
+  <si>
     <t>United Breweries Ltd.</t>
   </si>
   <si>
     <t>INE686F01025</t>
   </si>
   <si>
-    <t>Procter &amp; Gamble Hygiene and Health Care Ltd.</t>
-  </si>
-  <si>
-    <t>INE179A01014</t>
-  </si>
-  <si>
-    <t>ITC Hotels Ltd</t>
-  </si>
-  <si>
-    <t>INE379A01028</t>
-  </si>
-  <si>
-    <t>Leisure Services</t>
-  </si>
-  <si>
-    <t>Balrampur Chini Mills Ltd.</t>
-  </si>
-  <si>
-    <t>INE119A01028</t>
+    <t>Emami Ltd.</t>
+  </si>
+  <si>
+    <t>INE548C01032</t>
   </si>
   <si>
     <t>Unlisted</t>
@@ -232,7 +223,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -615,13 +606,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -639,7 +630,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="13030200"/>
+          <a:off x="666750" y="12839700"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -654,13 +645,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
+      <xdr:row>80</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -678,7 +669,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="15887700"/>
+          <a:off x="666750" y="15697200"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1012,7 +1003,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J80"/>
+  <dimension ref="B1:J79"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
@@ -1112,10 +1103,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>53597.95</v>
+        <v>55616.50000000001</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9999814290701999</v>
+        <v>0.9932221669863001</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1149,10 +1140,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>53597.95</v>
+        <v>55616.50000000001</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9999814290701999</v>
+        <v>0.9932221669863001</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1175,13 +1166,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>3678595</v>
+        <v>4300208</v>
       </c>
       <c r="G8" s="15">
-        <v>16461.71</v>
+        <v>17977.02</v>
       </c>
       <c r="H8" s="16">
-        <v>0.307127498174</v>
+        <v>0.3210409637494</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1204,13 +1195,13 @@
         <v>17</v>
       </c>
       <c r="F9" s="14">
-        <v>437380</v>
+        <v>438462</v>
       </c>
       <c r="G9" s="15">
-        <v>10798.04</v>
+        <v>10296.40</v>
       </c>
       <c r="H9" s="16">
-        <v>0.2014599340155</v>
+        <v>0.1838773155478</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1233,13 +1224,13 @@
         <v>22</v>
       </c>
       <c r="F10" s="14">
-        <v>176447</v>
+        <v>177116</v>
       </c>
       <c r="G10" s="15">
-        <v>4081.57</v>
+        <v>4244.05</v>
       </c>
       <c r="H10" s="16">
-        <v>0.0761501923385</v>
+        <v>0.0757919778806</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1262,13 +1253,13 @@
         <v>25</v>
       </c>
       <c r="F11" s="14">
-        <v>659917</v>
+        <v>321797</v>
       </c>
       <c r="G11" s="15">
-        <v>3542.10</v>
+        <v>3560.04</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0660852554978</v>
+        <v>0.0635766479976</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1288,16 +1279,16 @@
         <v>13</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F12" s="14">
-        <v>320469</v>
+        <v>58267</v>
       </c>
       <c r="G12" s="15">
-        <v>3283.69</v>
+        <v>3210.80</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0612640785482</v>
+        <v>0.0573397774718</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1308,25 +1299,25 @@
     </row>
     <row r="13" spans="2:10" ht="15" customHeight="1">
       <c r="B13" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="D13" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>22</v>
-      </c>
       <c r="F13" s="14">
-        <v>58062</v>
+        <v>662805</v>
       </c>
       <c r="G13" s="15">
-        <v>2978.38</v>
+        <v>3154.62</v>
       </c>
       <c r="H13" s="16">
-        <v>0.055567884382</v>
+        <v>0.0563364920917</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1349,13 +1340,13 @@
         <v>33</v>
       </c>
       <c r="F14" s="14">
-        <v>185413</v>
+        <v>236655</v>
       </c>
       <c r="G14" s="15">
-        <v>2078.94</v>
+        <v>2914.17</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0387869571905</v>
+        <v>0.0520424378083</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1375,16 +1366,16 @@
         <v>13</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F15" s="14">
-        <v>145296</v>
+        <v>145943</v>
       </c>
       <c r="G15" s="15">
-        <v>2069.02</v>
+        <v>2218.48</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0386018789221</v>
+        <v>0.0396185217159</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1404,16 +1395,16 @@
         <v>13</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F16" s="14">
-        <v>65203</v>
+        <v>260775</v>
       </c>
       <c r="G16" s="15">
-        <v>1839.74</v>
+        <v>1868.32</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0343241828151</v>
+        <v>0.0333652214545</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1433,16 +1424,16 @@
         <v>13</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F17" s="14">
-        <v>259597</v>
+        <v>65086</v>
       </c>
       <c r="G17" s="15">
-        <v>1740.99</v>
+        <v>1598.45</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0324817958186</v>
+        <v>0.028545772798</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1465,13 +1456,13 @@
         <v>33</v>
       </c>
       <c r="F18" s="14">
-        <v>290885</v>
+        <v>291391</v>
       </c>
       <c r="G18" s="15">
-        <v>1541.25</v>
+        <v>1407.27</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0287552299585</v>
+        <v>0.0251316022931</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1491,16 +1482,16 @@
         <v>13</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F19" s="14">
-        <v>38469</v>
+        <v>38600</v>
       </c>
       <c r="G19" s="15">
-        <v>838.01</v>
+        <v>977.66</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0156348225515</v>
+        <v>0.0174594514896</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1523,13 +1514,13 @@
         <v>25</v>
       </c>
       <c r="F20" s="14">
-        <v>37040</v>
+        <v>54782</v>
       </c>
       <c r="G20" s="15">
-        <v>794.88</v>
+        <v>915.57</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0148301425397</v>
+        <v>0.0163506229163</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -1549,16 +1540,16 @@
         <v>13</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F21" s="14">
-        <v>4658</v>
+        <v>35629</v>
       </c>
       <c r="G21" s="15">
-        <v>675.44</v>
+        <v>704.31</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0126017404854</v>
+        <v>0.0125778555721</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -1578,16 +1569,16 @@
         <v>13</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="F22" s="14">
-        <v>367597</v>
+        <v>97456</v>
       </c>
       <c r="G22" s="15">
-        <v>599</v>
+        <v>569.34</v>
       </c>
       <c r="H22" s="16">
-        <v>0.011175593022</v>
+        <v>0.0101675061996</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -1598,620 +1589,603 @@
     </row>
     <row r="23" spans="2:10" ht="15" customHeight="1">
       <c r="B23" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C23" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" ht="15" customHeight="1">
+      <c r="B24" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" ht="15" customHeight="1">
+      <c r="B25" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" ht="15" customHeight="1">
+      <c r="B26" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F23" s="14">
-        <v>56467</v>
-      </c>
-      <c r="G23" s="15">
-        <v>275.19</v>
-      </c>
-      <c r="H23" s="16">
-        <v>0.0051342428108</v>
-      </c>
-      <c r="I23" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J23" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" ht="15" customHeight="1">
-      <c r="B24" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J24" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="2:10" ht="15" customHeight="1">
-      <c r="B25" s="7" t="s">
+      <c r="C26" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" ht="15" customHeight="1">
+      <c r="B27" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J27" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" ht="15" customHeight="1">
+      <c r="B28" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J28" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" ht="15" customHeight="1">
+      <c r="B29" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J29" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" ht="15" customHeight="1">
+      <c r="B30" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C25" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25" s="9" t="s">
+      <c r="C30" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H30" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" ht="15" customHeight="1">
+      <c r="B31" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J31" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" ht="15" customHeight="1">
+      <c r="B32" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H25" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J25" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="2:10" ht="15" customHeight="1">
-      <c r="B26" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J26" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="2:10" ht="15" customHeight="1">
-      <c r="B27" s="7" t="s">
+      <c r="C32" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J32" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" ht="15" customHeight="1">
+      <c r="B33" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J33" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" ht="15" customHeight="1">
+      <c r="B34" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J27" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="2:10" ht="15" customHeight="1">
-      <c r="B28" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J28" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10" ht="15" customHeight="1">
-      <c r="B29" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J29" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10" ht="15" customHeight="1">
-      <c r="B30" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J30" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10" ht="15" customHeight="1">
-      <c r="B31" s="7" t="s">
+      <c r="C34" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J34" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" ht="15" customHeight="1">
+      <c r="B35" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J35" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" ht="15" customHeight="1">
+      <c r="B36" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C31" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="I31" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J31" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10" ht="15" customHeight="1">
-      <c r="B32" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J32" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33" spans="2:10" ht="15" customHeight="1">
-      <c r="B33" s="7" t="s">
+      <c r="C36" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J36" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" ht="15" customHeight="1">
+      <c r="B37" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J37" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" ht="15" customHeight="1">
+      <c r="B38" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C33" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J33" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10" ht="15" customHeight="1">
-      <c r="B34" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J34" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35" spans="2:10" ht="15" customHeight="1">
-      <c r="B35" s="7" t="s">
+      <c r="C38" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H38" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J38" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" ht="15" customHeight="1">
+      <c r="B39" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J39" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" ht="15" customHeight="1">
+      <c r="B40" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C35" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J35" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" spans="2:10" ht="15" customHeight="1">
-      <c r="B36" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J36" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="37" spans="2:10" ht="15" customHeight="1">
-      <c r="B37" s="7" t="s">
+      <c r="C40" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H40" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I40" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J40" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" ht="15" customHeight="1">
+      <c r="B41" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J41" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" ht="15" customHeight="1">
+      <c r="B42" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C37" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="I37" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J37" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="38" spans="2:10" ht="15" customHeight="1">
-      <c r="B38" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J38" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" spans="2:10" ht="15" customHeight="1">
-      <c r="B39" s="7" t="s">
+      <c r="C42" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H42" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J42" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" ht="15" customHeight="1">
+      <c r="B43" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J43" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" ht="15" customHeight="1">
+      <c r="B44" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G39" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="I39" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J39" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40" spans="2:10" ht="15" customHeight="1">
-      <c r="B40" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J40" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="41" spans="2:10" ht="15" customHeight="1">
-      <c r="B41" s="7" t="s">
+      <c r="C44" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H44" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I44" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J44" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" ht="15" customHeight="1">
+      <c r="B45" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" ht="15" customHeight="1">
+      <c r="B46" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C41" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G41" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="I41" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J41" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" spans="2:10" ht="15" customHeight="1">
-      <c r="B42" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J42" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43" spans="2:10" ht="15" customHeight="1">
-      <c r="B43" s="7" t="s">
+      <c r="C46" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H46" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I46" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" ht="15" customHeight="1">
+      <c r="B47" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J47" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" ht="15" customHeight="1">
+      <c r="B48" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C43" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F43" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G43" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="I43" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J43" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="44" spans="2:10" ht="15" customHeight="1">
-      <c r="B44" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J44" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="45" spans="2:10" ht="15" customHeight="1">
-      <c r="B45" s="7" t="s">
+      <c r="C48" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H48" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I48" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J48" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" ht="15" customHeight="1">
+      <c r="B49" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J49" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" ht="15" customHeight="1">
+      <c r="B50" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C45" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="I45" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J45" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46" spans="2:10" ht="15" customHeight="1">
-      <c r="B46" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J46" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="2:10" ht="15" customHeight="1">
-      <c r="B47" s="7" t="s">
+      <c r="C50" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G50" s="9">
+        <v>425.81</v>
+      </c>
+      <c r="H50" s="10">
+        <v>0.0076042888517</v>
+      </c>
+      <c r="I50" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J50" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" ht="15" customHeight="1">
+      <c r="B51" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J51" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" ht="15" customHeight="1">
+      <c r="B52" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C47" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F47" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G47" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="I47" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J47" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48" spans="2:10" ht="15" customHeight="1">
-      <c r="B48" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J48" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="49" spans="2:10" ht="15" customHeight="1">
-      <c r="B49" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F49" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G49" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="I49" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J49" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="50" spans="2:10" ht="15" customHeight="1">
-      <c r="B50" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J50" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="51" spans="2:10" ht="15" customHeight="1">
-      <c r="B51" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G51" s="9">
-        <v>11.13</v>
-      </c>
-      <c r="H51" s="10">
-        <v>0.0002076533394</v>
-      </c>
-      <c r="I51" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J51" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="52" spans="2:10" ht="15" customHeight="1">
-      <c r="B52" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J52" s="11" t="s">
+      <c r="C52" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F52" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G52" s="18">
+        <v>-46.278247399990505</v>
+      </c>
+      <c r="H52" s="19">
+        <v>-0.00082645583895044</v>
+      </c>
+      <c r="I52" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J52" s="20" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1">
       <c r="B53" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="C53" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F53" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G53" s="18">
+        <v>55996.0317526</v>
+      </c>
+      <c r="H53" s="19">
+        <v>0.9999999999990495</v>
+      </c>
+      <c r="I53" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J53" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" ht="15" customHeight="1">
+      <c r="B56" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C56" s="21"/>
+      <c r="D56" s="21"/>
+      <c r="E56" s="21"/>
+      <c r="F56" s="21"/>
+      <c r="G56" s="21"/>
+      <c r="H56" s="21"/>
+      <c r="I56" s="21"/>
+    </row>
+    <row r="57" spans="2:8" ht="15" customHeight="1">
+      <c r="B57" s="13" t="s">
         <v>67</v>
-      </c>
-      <c r="C53" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D53" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E53" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F53" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G53" s="18">
-        <v>-10.134617799994885</v>
-      </c>
-      <c r="H53" s="19">
-        <v>-0.00018908241062818657</v>
-      </c>
-      <c r="I53" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J53" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="54" spans="2:10" ht="15" customHeight="1">
-      <c r="B54" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="C54" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D54" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E54" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F54" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G54" s="18">
-        <v>53598.9453822</v>
-      </c>
-      <c r="H54" s="19">
-        <v>0.9999999999989716</v>
-      </c>
-      <c r="I54" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J54" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="57" spans="2:9" ht="15" customHeight="1">
-      <c r="B57" s="13" t="s">
-        <v>69</v>
       </c>
       <c r="C57" s="21"/>
       <c r="D57" s="21"/>
@@ -2219,11 +2193,10 @@
       <c r="F57" s="21"/>
       <c r="G57" s="21"/>
       <c r="H57" s="21"/>
-      <c r="I57" s="21"/>
-    </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1">
-      <c r="B58" s="13" t="s">
-        <v>70</v>
+    </row>
+    <row r="58" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B58" s="22" t="s">
+        <v>68</v>
       </c>
       <c r="C58" s="21"/>
       <c r="D58" s="21"/>
@@ -2234,7 +2207,7 @@
     </row>
     <row r="59" spans="2:8" ht="27.6" customHeight="1">
       <c r="B59" s="22" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C59" s="21"/>
       <c r="D59" s="21"/>
@@ -2245,7 +2218,7 @@
     </row>
     <row r="60" spans="2:8" ht="27.6" customHeight="1">
       <c r="B60" s="22" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C60" s="21"/>
       <c r="D60" s="21"/>
@@ -2254,42 +2227,31 @@
       <c r="G60" s="21"/>
       <c r="H60" s="21"/>
     </row>
-    <row r="61" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B61" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="C61" s="21"/>
-      <c r="D61" s="21"/>
-      <c r="E61" s="21"/>
-      <c r="F61" s="21"/>
-      <c r="G61" s="21"/>
-      <c r="H61" s="21"/>
-    </row>
-    <row r="64" ht="15">
-      <c r="B64" s="21" t="s">
-        <v>74</v>
+    <row r="63" ht="15">
+      <c r="B63" s="21" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="78" ht="15">
+      <c r="B78" s="21" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="79" ht="15">
       <c r="B79" s="21" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="80" ht="15">
-      <c r="B80" s="21" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="B58:H58"/>
     <mergeCell ref="B59:H59"/>
     <mergeCell ref="B60:H60"/>
-    <mergeCell ref="B61:H61"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B57:I57"/>
-    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="B56:I56"/>
+    <mergeCell ref="B57:H57"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
